--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.64581</v>
+        <v>16.58853</v>
       </c>
       <c r="D2" t="n">
-        <v>16.29874</v>
+        <v>16.33197</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79005</v>
+        <v>16.50033</v>
       </c>
       <c r="F2" t="n">
-        <v>42.10827</v>
+        <v>42.17946</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05104</v>
+        <v>0.04922</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82724</v>
+        <v>1.81328</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.66961</v>
+        <v>16.69267</v>
       </c>
       <c r="D3" t="n">
-        <v>16.65624</v>
+        <v>16.27344</v>
       </c>
       <c r="E3" t="n">
-        <v>16.66114</v>
+        <v>16.47219</v>
       </c>
       <c r="F3" t="n">
-        <v>41.81449</v>
+        <v>42.39675</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05048</v>
+        <v>0.04995</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81068</v>
+        <v>1.7762</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81449</v>
+        <v>16.72725</v>
       </c>
       <c r="D4" t="n">
-        <v>16.74684</v>
+        <v>16.28927</v>
       </c>
       <c r="E4" t="n">
-        <v>16.45519</v>
+        <v>16.65445</v>
       </c>
       <c r="F4" t="n">
-        <v>42.7939</v>
+        <v>41.94995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05111</v>
+        <v>0.04933</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85406</v>
+        <v>1.83424</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.83215</v>
+        <v>16.76785</v>
       </c>
       <c r="D6" t="n">
-        <v>15.97369</v>
+        <v>15.85452</v>
       </c>
       <c r="E6" t="n">
-        <v>16.69582</v>
+        <v>16.28499</v>
       </c>
       <c r="F6" t="n">
-        <v>21.33461</v>
+        <v>21.69534</v>
       </c>
       <c r="G6" t="n">
-        <v>34.22021</v>
+        <v>33.34746</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.80568</v>
+        <v>16.50235</v>
       </c>
       <c r="D7" t="n">
-        <v>15.67074</v>
+        <v>16.06998</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4437</v>
+        <v>16.20978</v>
       </c>
       <c r="F7" t="n">
-        <v>21.52737</v>
+        <v>21.44327</v>
       </c>
       <c r="G7" t="n">
-        <v>34.15187</v>
+        <v>33.93192</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.40664</v>
+        <v>16.72827</v>
       </c>
       <c r="D8" t="n">
-        <v>15.64209</v>
+        <v>16.00539</v>
       </c>
       <c r="E8" t="n">
-        <v>16.47424</v>
+        <v>16.18048</v>
       </c>
       <c r="F8" t="n">
-        <v>21.41246</v>
+        <v>21.41111</v>
       </c>
       <c r="G8" t="n">
-        <v>33.32337</v>
+        <v>34.31589</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.59502</v>
+        <v>0.60494</v>
       </c>
       <c r="D10" t="n">
-        <v>1.08002</v>
+        <v>1.09986</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60707</v>
+        <v>0.60284</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11273</v>
+        <v>1.13861</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5924700000000001</v>
+        <v>0.6061800000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10696</v>
+        <v>1.08697</v>
       </c>
     </row>
   </sheetData>
